--- a/Item_道具表.xlsx
+++ b/Item_道具表.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>类名</t>
   </si>
@@ -50,6 +50,12 @@
     <t>是否启用</t>
   </si>
   <si>
+    <t>买价</t>
+  </si>
+  <si>
+    <t>卖价</t>
+  </si>
+  <si>
     <t>Index</t>
   </si>
   <si>
@@ -72,6 +78,12 @@
   </si>
   <si>
     <t>Enable</t>
+  </si>
+  <si>
+    <t>BuyPrice</t>
+  </si>
+  <si>
+    <t>SellPrice</t>
   </si>
   <si>
     <t>client</t>
@@ -183,7 +195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -227,83 +239,107 @@
       <c r="H3" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="I3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -311,7 +347,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" s="0">
         <v>1</v>
@@ -326,10 +362,16 @@
         <v>0</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H7" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I7" s="0">
+        <v>10</v>
+      </c>
+      <c r="J7" s="0">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -337,7 +379,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" s="0">
         <v>2</v>
@@ -352,10 +394,16 @@
         <v>0</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H8" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I8" s="0">
+        <v>8</v>
+      </c>
+      <c r="J8" s="0">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -363,7 +411,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" s="0">
         <v>3</v>
@@ -378,10 +426,16 @@
         <v>0</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H9" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I9" s="0">
+        <v>30</v>
+      </c>
+      <c r="J9" s="0">
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -389,7 +443,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="0">
         <v>4</v>
@@ -404,10 +458,16 @@
         <v>0</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H10" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I10" s="0">
+        <v>20</v>
+      </c>
+      <c r="J10" s="0">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -415,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" s="0">
         <v>5</v>
@@ -430,10 +490,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H11" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I11" s="0">
+        <v>10</v>
+      </c>
+      <c r="J11" s="0">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -441,7 +507,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C12" s="0">
         <v>1</v>
@@ -456,10 +522,16 @@
         <v>0</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H12" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I12" s="0">
+        <v>10</v>
+      </c>
+      <c r="J12" s="0">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -467,7 +539,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C13" s="0">
         <v>2</v>
@@ -482,10 +554,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H13" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I13" s="0">
+        <v>8</v>
+      </c>
+      <c r="J13" s="0">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -493,7 +571,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C14" s="0">
         <v>3</v>
@@ -508,10 +586,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H14" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I14" s="0">
+        <v>30</v>
+      </c>
+      <c r="J14" s="0">
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -519,7 +603,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C15" s="0">
         <v>4</v>
@@ -534,10 +618,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H15" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="I15" s="0">
+        <v>20</v>
+      </c>
+      <c r="J15" s="0">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
